--- a/order_forms/022_structural_engineering_quotation_form--order_forms.xlsx
+++ b/order_forms/022_structural_engineering_quotation_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Client's First Name</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Client's Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -669,7 +669,7 @@
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>first_name_1</t>
+          <t>first_name_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>First Name</t>
+          <t>Client Contact 2 First Name</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>last_name_1</t>
+          <t>last_name_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -761,7 +761,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>contact_number_1</t>
+          <t>contact_number_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -784,47 +784,47 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>structural_engineering_quotation_form_additional_comments_1</t>
+          <t>project_type_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Project Type 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>project_type_1</t>
+          <t>project_location_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Project Type</t>
+          <t>Project Location 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>project_location_1</t>
+          <t>structural_engineering_quotation_form_additional_comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Project Location</t>
+          <t>Additional Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>structural_engineering_quotation_form_additional_comments_1</t>
+          <t>client_contact_3_first_name</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Additional Comments</t>
+          <t>Client Contact 3 First Name</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_name_2</t>
+          <t>client_contact_3_last_name</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Client Contact 2</t>
+          <t>Client Contact 3 Last Name</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>last_name_2</t>
+          <t>contact_number_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Last Name</t>
+          <t>Contact Number 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,159 +929,21 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>contact_number_2</t>
+          <t>project_type_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Contact Number</t>
+          <t>Project Type 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>structural_engineering_quotation_form_additional_comments_2</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>project_type_2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Project Type</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>project_location_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Project Location</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>structural_engineering_quotation_form_additional_comments_2</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>first_name_3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Client Contact 3</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>last_name_3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Last Name</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1102,8 +964,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +993,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1010,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1165,114 +1027,114 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>project_type_1_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>project_type_1_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>project_type_1_choices</t>
+          <t>project_type_2_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>project_type_2_choices</t>
+          <t>project_type_3_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>project_type_2_choices</t>
+          <t>project_type_3_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>project_type_2_choices</t>
+          <t>project_type_3_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'industrial'}</t>
+          <t>industrial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Industrial'}</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
